--- a/20-excel-based/models/100-workflow-model.xlsx
+++ b/20-excel-based/models/100-workflow-model.xlsx
@@ -2282,7 +2282,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>974c7560-eb4f-4ddf-8741-058141c104fc</t>
+          <t>aa8b109a-6788-45c0-95dd-aaf9b60511e8</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>done||rollback</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gfemsmereview</t>
+          <t>gfemsmereview||sptreview</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>EPC SME Review</t>
+          <t>EPC SME Review Pending</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dcca7969-95c5-433e-9fbe-da1247cfdfd5</t>
+          <t>b2a59a2f-d892-4130-90dd-7ebb0c923808</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>done||rollback</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>inventoryreviewpending</t>
+          <t>inventoryreviewpending||epcsmereview</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GF EM SME Review</t>
+          <t>GF EM SME Review Pending</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>e9b613db-c1ae-41a7-95fb-c12dacb0bb97</t>
+          <t>61d8fc13-da97-49d7-b4fe-3c836a42f653</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4219b035-52c7-4666-9189-0fb68ca2694f</t>
+          <t>6ff1e1b8-b9da-4635-93b8-1030b3532778</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>approve||reject</t>
+          <t>approve||reject||rollback</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>[STOP]||inventoryreviewpending</t>
+          <t>[STOP]||inventoryreviewpending||gfemsmereview</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SPT Review</t>
+          <t>SPT Review Pending</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>9cd43e82-340b-492b-94f0-a17514c91a81</t>
+          <t>1a7157b1-82ae-45da-a567-f68750c383d1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>done||rollback</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>emreviewpending</t>
+          <t>emreviewpending||emreviewpending</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>b75fd78a-f481-44e9-aedc-66a4c27cd366</t>
+          <t>10442ab7-91d3-422d-8f28-817ee0119aad</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>approve</t>
+          <t>approve||rollback</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>mmreviewpending</t>
+          <t>mmreviewpending||sptreviewpending</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>83b53414-fffe-404c-b00d-d9896ea807b3</t>
+          <t>04dedc81-7ac1-4899-acee-a9a821b4af70</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>approve</t>
+          <t>approve||rollback</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>epcenrichmentpo</t>
+          <t>epcenrichmentpo||emreviewpending</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>f459cadd-6e7b-4ff8-afee-26414e1e61f6</t>
+          <t>e9049a77-4cbb-4698-93c4-c8cdadaa49c2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>approve</t>
+          <t>approve||rollback</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[STOP]</t>
+          <t>[STOP]||emreviewpending</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -3637,7 +3637,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B2:H17"/>
+  <dimension ref="B2:H24"/>
   <sheetFormatPr defaultRowHeight="21.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="12.33203125"/>
@@ -3981,12 +3981,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>gfemsmereview</t>
+          <t>epcsmereview</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>rollback</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Rollback</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>inventoryreviewpending</t>
+          <t>gfemsmereview</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sptreview</t>
+          <t>gfemsmereview</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>approve</t>
+          <t>rollback</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Rollback</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4092,12 +4092,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sptreview</t>
+          <t>inventoryreviewpending</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>reject</t>
+          <t>done</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mandatory</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Reject</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -4124,17 +4124,17 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>prverification</t>
+          <t>spirverificationgfwf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sptreviewpending</t>
+          <t>sptreview</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>done</t>
+          <t>approve</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Approve</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4161,17 +4161,17 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>prverification</t>
+          <t>spirverificationgfwf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>emreviewpending</t>
+          <t>sptreview</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>approve</t>
+          <t>reject</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Mandatory</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Reject</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4198,17 +4198,17 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>prverification</t>
+          <t>spirverificationgfwf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>mmreviewpending</t>
+          <t>sptreview</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>approve</t>
+          <t>rollback</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Approve</t>
+          <t>Rollback</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -4240,32 +4240,291 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>sptreviewpending</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prverification</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sptreviewpending</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rollback</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prverification</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>emreviewpending</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>approve</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prverification</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>emreviewpending</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Rollback</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prverification</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mmreviewpending</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>approve</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Approve</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prverification</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mmreviewpending</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rollback</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prverification</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>epcenrichmentpo</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>approve</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Approve</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prverification</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>epcenrichmentpo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>rollback</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rollback</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
